--- a/ML-Entrees/ig/StructureDefinition-fr-lm-immunisation.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-immunisation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T09:43:36+00:00</t>
+    <t>2026-04-08T13:03:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Vaccination</t>
+    <t>Entrée Vaccination</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -408,13 +408,14 @@
     <t>fr-lm-entry.header.langue</t>
   </si>
   <si>
-    <t>fr-lm-immunisation.header.code</t>
-  </si>
-  <si>
-    <t>Type de l'entrée</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.code</t>
+    <t>fr-lm-immunisation.status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code
+</t>
+  </si>
+  <si>
+    <t>Statut de la vaccination (réalisé, non fait, ...).</t>
   </si>
   <si>
     <t>fr-lm-immunisation.periodOfImmunisation</t>
@@ -2473,7 +2474,7 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>79</v>
@@ -2488,13 +2489,13 @@
         <v>73</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2545,10 +2546,10 @@
         <v>73</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH16" t="s" s="2">
         <v>79</v>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-immunisation.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-immunisation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T13:03:38+00:00</t>
+    <t>2026-04-08T14:07:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-immunisation.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-immunisation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T14:07:03+00:00</t>
+    <t>2026-04-09T12:24:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-immunisation.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-immunisation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T12:24:05+00:00</t>
+    <t>2026-04-13T08:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-immunisation.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-immunisation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T08:58:24+00:00</t>
+    <t>2026-04-13T09:04:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-immunisation.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-immunisation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T09:04:52+00:00</t>
+    <t>2026-04-14T07:59:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-immunisation.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-immunisation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1067" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1067" uniqueCount="191">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T07:59:58+00:00</t>
+    <t>2026-04-16T07:11:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -304,39 +304,43 @@
     <t>fr-lm-immunisation.header.author[x].authorProfessional</t>
   </si>
   <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure-auteur
+</t>
+  </si>
+  <si>
+    <t>L'auteur est un professionnel de santé</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorProfessional</t>
+  </si>
+  <si>
+    <t>fr-lm-immunisation.header.author[x].authorOrganisation</t>
+  </si>
+  <si>
+    <t>L'auteur est une organisation</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorOrganisation</t>
+  </si>
+  <si>
+    <t>fr-lm-immunisation.header.author[x].authorDevice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-systeme-structure-auteur
+</t>
+  </si>
+  <si>
+    <t>L'auteur est un système</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorDevice</t>
+  </si>
+  <si>
+    <t>fr-lm-immunisation.header.performer</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure
 </t>
-  </si>
-  <si>
-    <t>L'auteur est un professionnel de santé</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.author[x].authorProfessional</t>
-  </si>
-  <si>
-    <t>fr-lm-immunisation.header.author[x].authorOrganisation</t>
-  </si>
-  <si>
-    <t>L'auteur est une organisation</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.author[x].authorOrganisation</t>
-  </si>
-  <si>
-    <t>fr-lm-immunisation.header.author[x].authorDevice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-systeme-structure-auteur
-</t>
-  </si>
-  <si>
-    <t>L'auteur est un système</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.author[x].authorDevice</t>
-  </si>
-  <si>
-    <t>fr-lm-immunisation.header.performer</t>
   </si>
   <si>
     <t>Exécutant (performer)</t>
@@ -1889,13 +1893,13 @@
         <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1946,7 +1950,7 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
@@ -1963,10 +1967,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1989,13 +1993,13 @@
         <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2046,7 +2050,7 @@
         <v>73</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>74</v>
@@ -2063,10 +2067,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2089,13 +2093,13 @@
         <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2146,7 +2150,7 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
@@ -2163,10 +2167,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2189,13 +2193,13 @@
         <v>73</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2246,7 +2250,7 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
@@ -2263,10 +2267,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2289,13 +2293,13 @@
         <v>73</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2346,7 +2350,7 @@
         <v>73</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
@@ -2363,10 +2367,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2389,13 +2393,13 @@
         <v>73</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2446,7 +2450,7 @@
         <v>73</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>74</v>
@@ -2463,10 +2467,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2489,13 +2493,13 @@
         <v>73</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2546,7 +2550,7 @@
         <v>73</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -2563,10 +2567,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2589,13 +2593,13 @@
         <v>73</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2646,7 +2650,7 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -2658,15 +2662,15 @@
         <v>73</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2689,13 +2693,13 @@
         <v>73</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2746,7 +2750,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
@@ -2763,14 +2767,14 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -2789,16 +2793,16 @@
         <v>73</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -2836,19 +2840,19 @@
         <v>73</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
@@ -2860,15 +2864,15 @@
         <v>73</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2891,16 +2895,16 @@
         <v>73</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -2950,7 +2954,7 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -2967,10 +2971,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2993,13 +2997,13 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3050,7 +3054,7 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>74</v>
@@ -3062,15 +3066,15 @@
         <v>73</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3093,13 +3097,13 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3150,7 +3154,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>74</v>
@@ -3167,10 +3171,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3193,13 +3197,13 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3250,7 +3254,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
@@ -3267,10 +3271,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3293,13 +3297,13 @@
         <v>73</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3350,7 +3354,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
@@ -3367,10 +3371,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3393,13 +3397,13 @@
         <v>73</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3450,7 +3454,7 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -3467,10 +3471,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3493,13 +3497,13 @@
         <v>73</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3550,7 +3554,7 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>74</v>
@@ -3567,10 +3571,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3593,13 +3597,13 @@
         <v>73</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3650,7 +3654,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>
@@ -3667,10 +3671,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3693,13 +3697,13 @@
         <v>73</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3750,7 +3754,7 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
@@ -3767,10 +3771,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3793,13 +3797,13 @@
         <v>73</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3850,7 +3854,7 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
@@ -3867,10 +3871,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3893,13 +3897,13 @@
         <v>73</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -3950,7 +3954,7 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
@@ -3967,10 +3971,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -3993,13 +3997,13 @@
         <v>73</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4050,7 +4054,7 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
@@ -4067,10 +4071,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4093,13 +4097,13 @@
         <v>73</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4150,7 +4154,7 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>74</v>
@@ -4167,10 +4171,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4193,13 +4197,13 @@
         <v>73</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4250,7 +4254,7 @@
         <v>73</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>74</v>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-immunisation.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-immunisation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1067" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="203">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T07:11:11+00:00</t>
+    <t>2026-04-24T08:31:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -304,7 +304,7 @@
     <t>fr-lm-immunisation.header.author[x].authorProfessional</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure-auteur
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-health-professional
 </t>
   </si>
   <si>
@@ -317,6 +317,10 @@
     <t>fr-lm-immunisation.header.author[x].authorOrganisation</t>
   </si>
   <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-organisation
+</t>
+  </si>
+  <si>
     <t>L'auteur est une organisation</t>
   </si>
   <si>
@@ -326,7 +330,7 @@
     <t>fr-lm-immunisation.header.author[x].authorDevice</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-systeme-structure-auteur
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-device
 </t>
   </si>
   <si>
@@ -336,36 +340,59 @@
     <t>fr-lm-entry.header.author[x].authorDevice</t>
   </si>
   <si>
-    <t>fr-lm-immunisation.header.performer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure
-</t>
+    <t>fr-lm-immunisation.header.performer[x]</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-health-professional
+https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-organisation</t>
   </si>
   <si>
     <t>Exécutant (performer)</t>
   </si>
   <si>
-    <t>fr-lm-entry.header.performer</t>
-  </si>
-  <si>
-    <t>fr-lm-immunisation.header.participant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-participant-corps
-</t>
+    <t>fr-lm-entry.header.performer[x]</t>
+  </si>
+  <si>
+    <t>fr-lm-immunisation.header.participant[x]</t>
   </si>
   <si>
     <t>Participant</t>
   </si>
   <si>
-    <t>fr-lm-entry.header.participant</t>
+    <t>fr-lm-entry.header.participant[x]</t>
+  </si>
+  <si>
+    <t>fr-lm-immunisation.header.participant[x].participantProfessional</t>
+  </si>
+  <si>
+    <t>Le participant est un professionnel de santé</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x].participantProfessional</t>
+  </si>
+  <si>
+    <t>fr-lm-immunisation.header.participant[x].participantOrganisation</t>
+  </si>
+  <si>
+    <t>Le participant est une organisation</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x].participantOrganisation</t>
+  </si>
+  <si>
+    <t>fr-lm-immunisation.header.participant[x].participantDevice</t>
+  </si>
+  <si>
+    <t>Le participant est un système</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x].participantDevice</t>
   </si>
   <si>
     <t>fr-lm-immunisation.header.informant</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-informateur
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-informant
 </t>
   </si>
   <si>
@@ -388,11 +415,29 @@
     <t>fr-lm-entry.header.date</t>
   </si>
   <si>
-    <t>fr-lm-immunisation.header.source</t>
+    <t>fr-lm-immunisation.header.status</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
 </t>
+  </si>
+  <si>
+    <t>Statut de la vaccination (réalisé, non fait, ...).</t>
+  </si>
+  <si>
+    <t>Statut de l'acte</t>
+  </si>
+  <si>
+    <t>jdv-hl7-v3-ActStatus-cisis (2.16.840.1.113883.1.11.15933)</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActStatus-cisis</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.status</t>
+  </si>
+  <si>
+    <t>fr-lm-immunisation.header.source</t>
   </si>
   <si>
     <t>Source</t>
@@ -410,16 +455,6 @@
   </si>
   <si>
     <t>fr-lm-entry.header.langue</t>
-  </si>
-  <si>
-    <t>fr-lm-immunisation.status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">code
-</t>
-  </si>
-  <si>
-    <t>Statut de la vaccination (réalisé, non fait, ...).</t>
   </si>
   <si>
     <t>fr-lm-immunisation.periodOfImmunisation</t>
@@ -915,11 +950,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ33"/>
+  <dimension ref="A1:AJ36"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="45.5390625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="45.5390625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="52.25" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="52.25" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="10.83984375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -942,14 +977,14 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="16.828125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="47.0546875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="52.58203125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="41.87890625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="45.68359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -1693,13 +1728,13 @@
         <v>73</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1750,7 +1785,7 @@
         <v>73</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>74</v>
@@ -1767,10 +1802,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1793,13 +1828,13 @@
         <v>73</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1850,7 +1885,7 @@
         <v>73</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>74</v>
@@ -1867,10 +1902,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1893,13 +1928,13 @@
         <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1950,7 +1985,7 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
@@ -1967,10 +2002,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1993,7 +2028,7 @@
         <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="L11" t="s" s="2">
         <v>111</v>
@@ -2093,13 +2128,13 @@
         <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="L12" t="s" s="2">
-        <v>115</v>
-      </c>
       <c r="M12" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2150,7 +2185,7 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
@@ -2167,10 +2202,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2181,7 +2216,7 @@
         <v>74</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>73</v>
@@ -2193,13 +2228,13 @@
         <v>73</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2250,13 +2285,13 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>73</v>
@@ -2267,10 +2302,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2281,7 +2316,7 @@
         <v>74</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>73</v>
@@ -2293,13 +2328,13 @@
         <v>73</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2350,13 +2385,13 @@
         <v>73</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>73</v>
@@ -2367,10 +2402,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2381,7 +2416,7 @@
         <v>74</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>73</v>
@@ -2393,13 +2428,13 @@
         <v>73</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2450,13 +2485,13 @@
         <v>73</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>73</v>
@@ -2467,10 +2502,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2478,7 +2513,7 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>79</v>
@@ -2493,13 +2528,13 @@
         <v>73</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2550,10 +2585,10 @@
         <v>73</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH16" t="s" s="2">
         <v>79</v>
@@ -2567,10 +2602,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2593,10 +2628,10 @@
         <v>73</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="L17" t="s" s="2">
-        <v>133</v>
       </c>
       <c r="M17" t="s" s="2">
         <v>133</v>
@@ -2629,10 +2664,10 @@
         <v>73</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>73</v>
+        <v>135</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>73</v>
@@ -2650,7 +2685,7 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -2662,15 +2697,15 @@
         <v>73</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>134</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2693,10 +2728,10 @@
         <v>73</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M18" t="s" s="2">
         <v>138</v>
@@ -2774,14 +2809,14 @@
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>141</v>
+        <v>73</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>73</v>
@@ -2793,17 +2828,15 @@
         <v>73</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>73</v>
@@ -2840,39 +2873,39 @@
         <v>73</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>146</v>
+        <v>73</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>147</v>
+        <v>73</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>148</v>
+        <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>134</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2895,17 +2928,15 @@
         <v>73</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>154</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>73</v>
@@ -2954,7 +2985,7 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -2966,15 +2997,15 @@
         <v>73</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>73</v>
+        <v>146</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2997,13 +3028,13 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3054,7 +3085,7 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>74</v>
@@ -3066,26 +3097,26 @@
         <v>73</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>161</v>
+        <v>73</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>73</v>
+        <v>153</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>73</v>
@@ -3097,15 +3128,17 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>118</v>
+        <v>154</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>156</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>73</v>
@@ -3142,39 +3175,39 @@
         <v>73</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>73</v>
+        <v>158</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>73</v>
+        <v>159</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>73</v>
+        <v>160</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>73</v>
+        <v>146</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3182,7 +3215,7 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>79</v>
@@ -3197,15 +3230,17 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>118</v>
+        <v>163</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="M23" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="N23" s="2"/>
+      <c r="N23" t="s" s="2">
+        <v>166</v>
+      </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>73</v>
@@ -3254,10 +3289,10 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>79</v>
@@ -3271,10 +3306,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3285,7 +3320,7 @@
         <v>74</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>73</v>
@@ -3297,13 +3332,13 @@
         <v>73</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>122</v>
+        <v>169</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3354,27 +3389,27 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>73</v>
+        <v>173</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3382,7 +3417,7 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>79</v>
@@ -3397,13 +3432,13 @@
         <v>73</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>169</v>
+        <v>127</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3454,10 +3489,10 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>79</v>
@@ -3471,10 +3506,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3497,13 +3532,13 @@
         <v>73</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3554,7 +3589,7 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>74</v>
@@ -3571,10 +3606,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3597,13 +3632,13 @@
         <v>73</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3654,7 +3689,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>
@@ -3671,10 +3706,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3682,7 +3717,7 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>79</v>
@@ -3697,13 +3732,13 @@
         <v>73</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3754,10 +3789,10 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>79</v>
@@ -3771,10 +3806,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3797,13 +3832,13 @@
         <v>73</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>179</v>
+        <v>131</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3854,7 +3889,7 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
@@ -3871,10 +3906,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3885,7 +3920,7 @@
         <v>74</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>73</v>
@@ -3897,13 +3932,13 @@
         <v>73</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -3954,13 +3989,13 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>73</v>
@@ -3971,10 +4006,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -3997,13 +4032,13 @@
         <v>73</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4054,7 +4089,7 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
@@ -4071,10 +4106,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4085,7 +4120,7 @@
         <v>74</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>73</v>
@@ -4097,13 +4132,13 @@
         <v>73</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4154,13 +4189,13 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>73</v>
@@ -4171,10 +4206,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4185,7 +4220,7 @@
         <v>74</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>73</v>
@@ -4197,13 +4232,13 @@
         <v>73</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>122</v>
+        <v>148</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4254,18 +4289,318 @@
         <v>73</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E34" s="2"/>
+      <c r="F34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K34" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
+      <c r="P34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q34" s="2"/>
+      <c r="R34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF34" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E35" s="2"/>
+      <c r="F35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G35" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="AI33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ33" t="s" s="2">
+      <c r="H35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K35" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
+      <c r="P35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q35" s="2"/>
+      <c r="R35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF35" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E36" s="2"/>
+      <c r="F36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K36" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q36" s="2"/>
+      <c r="R36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF36" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-immunisation.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-immunisation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T08:31:26+00:00</t>
+    <t>2026-04-24T12:30:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-immunisation.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-immunisation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T12:30:57+00:00</t>
+    <t>2026-04-24T12:43:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
